--- a/qwen3-asr-local/benchmark/lab_test_80_calls_urdu_roman_urdu.xlsx
+++ b/qwen3-asr-local/benchmark/lab_test_80_calls_urdu_roman_urdu.xlsx
@@ -3180,7 +3180,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3191,6 +3191,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3227,16 +3233,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -3565,7 +3571,7 @@
     <col min="10" max="10" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3597,7 +3603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="24.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="24">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -3685,7 +3691,7 @@
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -3741,7 +3747,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="24.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="24">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -3801,7 +3807,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="24.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="24">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -3973,7 +3979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="24.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="24">
       <c r="A15" s="1" t="s">
         <v>10</v>
       </c>
@@ -4201,7 +4207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="24.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="24">
       <c r="A23" s="1" t="s">
         <v>10</v>
       </c>
@@ -4317,7 +4323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="24.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="24">
       <c r="A27" s="1" t="s">
         <v>10</v>
       </c>
